--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-26).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-26).xlsx
@@ -935,13 +935,13 @@
     <t>214</t>
   </si>
   <si>
-    <t>20</t>
+    <t>17</t>
   </si>
   <si>
-    <t>R$ 3.985,87</t>
+    <t>R$ 3.962,86</t>
   </si>
   <si>
-    <t>44.0</t>
+    <t>43.7</t>
   </si>
   <si>
     <t>27.4</t>
@@ -953,13 +953,13 @@
     <t>18.0</t>
   </si>
   <si>
-    <t>6.6</t>
+    <t>6.7</t>
   </si>
   <si>
     <t>6.5</t>
   </si>
   <si>
-    <t>45.2%</t>
+    <t>45.4%</t>
   </si>
   <si>
     <t>19.1%</t>
@@ -6849,7 +6849,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6879,14 +6879,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>3357.6500000000001</v>
+      </c>
+      <c r="N36" s="6">
+        <v>39</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>4.5315324324324324</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>17.302173913043479</v>
+      </c>
+      <c r="R36" s="8">
+        <v>5.4289869565217392</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.52173913043478259</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9138,7 +9150,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9168,14 +9180,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1031.8699999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <v>8</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>3.4125000000000001</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>22.230549999999997</v>
+      </c>
+      <c r="R51" s="8">
+        <v>12.086116666666667</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14840,7 +14864,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14868,14 +14892,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>3034.8400000000001</v>
+      </c>
+      <c r="N89" s="6">
+        <v>32</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>5.2546875000000002</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>25.190738888888887</v>
+      </c>
+      <c r="R89" s="8">
+        <v>12.162747058823529</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.055555555555555552</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
